--- a/CBT_2021_1회/산업안전기사_2021_1회_문항등록.xlsx
+++ b/CBT_2021_1회/산업안전기사_2021_1회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1721,17 +1721,17 @@
       </c>
       <c r="AG5" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;여럿을 한꺼번에 조직적으로&lt;/strong&gt; 가르칠 수 있는 것이 Off JT 의 장점이다. 나머지 셋은 &lt;strong&gt;OJT&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT 와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;따로 자리를 마련해&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;몇 명&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 사람 또는 소수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여럿을 한꺼번에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개별 지도 · 업무의 계속성이 유지된다 · 효과가 곧 업무에 나타난다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조직적·체계적 · 전문 강사 · 훈련에만 전념 · 다른 직장과의 교류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;여럿을 한꺼번에 조직적으로&lt;/strong&gt; 가르칠 수 있는 것이 Off JT의 장점이다. 나머지 셋은 &lt;strong&gt;OJT&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;따로 자리를 마련해&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;몇 명&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 사람 또는 소수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여럿을 한꺼번에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개별 지도 · 업무의 계속성이 유지된다 · 효과가 곧 업무에 나타난다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조직적·체계적 · 전문 강사 · 훈련에만 전념 · 다른 직장과의 교류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH5" s="32" t="inlineStr">
         <is>
-          <t>① 개개인에 맞춘 지도훈련은 OJT 의 장점이다.&lt;br&gt;② 업무의 계속성이 끊어지지 않는 것도 그렇다.&lt;br&gt;④ 효과가 곧 업무에 나타나는 것도 그렇다.</t>
+          <t>① 개개인에 맞춘 지도훈련은 OJT의 장점이다.&lt;br&gt;② 업무의 계속성이 끊어지지 않는 것도 그렇다.&lt;br&gt;④ 효과가 곧 업무에 나타나는 것도 그렇다.</t>
         </is>
       </c>
       <c r="AI5" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OJT 와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「다수 · 일괄 · 조직적 · 체계적 · 전문 강사」&lt;/strong&gt;라는 낱말이 나오면 Off JT 다 — &lt;strong&gt;나머지는 모두 「우리 현장, 나 한 사람」&lt;/strong&gt;이라 OJT 다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;다수를 일괄 교육하면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;OJT와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「다수 · 일괄 · 조직적 · 체계적 · 전문 강사」&lt;/strong&gt;라는 낱말이 나오면 Off JT다 — &lt;strong&gt;나머지는 모두 「우리 현장, 나 한 사람」&lt;/strong&gt;이라 OJT다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;다수를 일괄 교육하면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AI8" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방독마스크의 등급&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「2 · 1 · 0.1」&lt;/strong&gt; 세 값이다 — &lt;strong&gt;저농도만 자릿수가 한 칸 내려간다&lt;/strong&gt;. &lt;strong&gt;0.5 로 바꿔 놓으면 등급 사이가 고르게 보여&lt;/strong&gt; 그럴듯하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;저농도는 100분의 0.1 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방독마스크의 등급&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「2 · 1 · 0.1」&lt;/strong&gt; 세 값이다 — &lt;strong&gt;저농도만 자릿수가 한 칸 내려간다&lt;/strong&gt;. &lt;strong&gt;0.5로 바꿔 놓으면 등급 사이가 고르게 보여&lt;/strong&gt; 그럴듯하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;저농도는 100분의 0.1 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AI11" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;관리그리드 이론&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;격자가 1 ~ 9 이므로 한가운데는 5&lt;/strong&gt;다 — &lt;strong&gt;(3,3)은 가운데가 아니다&lt;/strong&gt;. &lt;strong&gt;(9,9) 이상형이 가장 바람직&lt;/strong&gt; 하다는 것도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;타협형은 (5,5)&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;관리그리드 이론&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;격자가 1 ~ 9이므로 한가운데는 5&lt;/strong&gt;다 — &lt;strong&gt;(3,3)은 가운데가 아니다&lt;/strong&gt;. &lt;strong&gt;(9,9) 이상형이 가장 바람직&lt;/strong&gt; 하다는 것도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;타협형은 (5,5)&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AG15" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시행착오설&lt;/strong&gt;이 &lt;strong&gt;자극-반응(S-R) 이론&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;학습이론의 두 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;갈래&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이론&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;S-R 이론(자극-반응)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시행착오설(손다이크) · 조건반사설(파블로프) · 조작적 조건화설(스키너)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;행동주의&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인지 이론(형태설)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통찰설(쾰러) · 장설(레빈) · 기호형태설(톨만)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인지주의&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;차이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;S-R 은 「반복으로 굳는다」, 인지는 「전체를 깨닫는다」&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;시행착오설&lt;/strong&gt;이 &lt;strong&gt;자극-반응(S-R) 이론&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;학습이론의 두 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;갈래&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이론&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;S-R 이론(자극-반응)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시행착오설(손다이크) · 조건반사설(파블로프) · 조작적 조건화설(스키너)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;행동주의&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인지 이론(형태설)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통찰설(쾰러) · 장설(레빈) · 기호형태설(톨만)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인지주의&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;차이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;S-R은 「반복으로 굳는다」, 인지는 「전체를 깨닫는다」&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH15" s="32" t="inlineStr">
@@ -3527,17 +3527,17 @@
       </c>
       <c r="AG19" s="32" t="inlineStr">
         <is>
-          <t>$\text{도수율} = \dfrac{\text{연천인율}}{2.4} = \dfrac{10.8}{2.4} = 4.5$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;연천인율과 도수율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연천인율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{연간 재해자수}}{\text{연평균 근로자수}} \times 1 {,} 000$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{재해건수}}{\text{연근로시간수}} \times 10^{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연천인율 = 도수율 × 2.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1인이 연 2,400시간 근무한다고 볼 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10.8 ÷ 2.4 = 4.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\text{도수율} = \dfrac{\text{연천인율}}{2.4} = \dfrac{10.8}{2.4} = 4.5$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;연천인율과 도수율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연천인율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{연간 재해자수}}{\text{연평균 근로자수}} \times 1 {,} 000$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{재해건수}}{\text{연근로시간수}} \times 10^{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연천인율 = 도수율 × 2.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1인이 연 2,400시간 근무한다고 볼 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10.8 ÷ 2.4 = 4.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH19" s="32" t="inlineStr">
         <is>
-          <t>① 5.4 는 2 로 나눈 값이다.&lt;br&gt;③ 3.7 은 계산과 맞지 않는다.&lt;br&gt;④ 1.8 도 그렇다.</t>
+          <t>① 5.4는 2로 나눈 값이다.&lt;br&gt;③ 3.7은 계산과 맞지 않는다.&lt;br&gt;④ 1.8 도 그렇다.</t>
         </is>
       </c>
       <c r="AI19" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;연천인율과 도수율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;2.4 라는 수는 「1인 연간 2,400시간」&lt;/strong&gt;에서 나온다 — &lt;strong&gt;연천인율이 도수율보다 크므로 나눈다&lt;/strong&gt;. &lt;strong&gt;반대로 도수율에서 연천인율을 구하면 곱한다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;연천인율 = 도수율 × 2.4&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;연천인율과 도수율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;2.4라는 수는 「1인 연간 2,400시간」&lt;/strong&gt;에서 나온다 — &lt;strong&gt;연천인율이 도수율보다 크므로 나눈다&lt;/strong&gt;. &lt;strong&gt;반대로 도수율에서 연천인율을 구하면 곱한다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;연천인율 = 도수율 × 2.4&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="AG21" s="32" t="inlineStr">
         <is>
-          <t>$\text{연천인율} = \text{도수율} \times 2.4 = 10 \times 2.4 = 24$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;연천인율과 도수율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연천인율 → 도수율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;÷ 2.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율 → 연천인율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;× 2.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2.4 의 뿌리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{1 {,} 000}{10^{6}} \times 2 {,} 400 = 2.4$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1인 연간 2,400시간&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;결과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 × 2.4 = 24&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\text{연천인율} = \text{도수율} \times 2.4 = 10 \times 2.4 = 24$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;연천인율과 도수율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연천인율 → 도수율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;÷ 2.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율 → 연천인율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;× 2.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2.4의 뿌리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{1 {,} 000}{10^{6}} \times 2 {,} 400 = 2.4$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1인 연간 2,400시간&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;결과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 × 2.4 = 24&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH21" s="32" t="inlineStr">
         <is>
-          <t>① 2.4 는 배수 자체다.&lt;br&gt;② 5 는 계산과 맞지 않는다.&lt;br&gt;③ 12 도 그렇다.</t>
+          <t>① 2.4는 배수 자체다.&lt;br&gt;② 5는 계산과 맞지 않는다.&lt;br&gt;③ 12 도 그렇다.</t>
         </is>
       </c>
       <c r="AI21" s="32" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="U23" s="32" t="inlineStr">
         <is>
-          <t>그림과 같은 FT도에서 정상사상 T의 발생 확률은? (단, X1, X2, X3의 발생 확률은 각각 0.1, 0.15, 0.1 이다.)</t>
+          <t>그림과 같은 FT도에서 정상사상 T의 발생 확률은? (단, X1, X2, X3의 발생 확률은 각각 0.1, 0.15, 0.1이다.)</t>
         </is>
       </c>
       <c r="V23" s="32" t="inlineStr"/>
@@ -4047,17 +4047,17 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>정상사상 T 가 &lt;strong&gt;OR 게이트&lt;/strong&gt;이므로 &lt;strong&gt;여사건(일어나지 않을 확률)을 곱해&lt;/strong&gt; 구한다.$P ( T ) = 1 - ( 1 - 0.1 ) ( 1 - 0.15 ) ( 1 - 0.1 ) = 1 - 0.9 \times 0.85 \times 0.9 = 1 - 0.6885 = 0.3115$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;게이트별 확률 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P = P_{1} \times P_{2} \times \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나야&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;OR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P = 1 - ( 1 - P_{1} ) ( 1 - P_{2} ) \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하나만 일어나도&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$1 - 0.9 \times 0.85 \times 0.9 = 0.3115$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>정상사상 T가 &lt;strong&gt;OR 게이트&lt;/strong&gt;이므로 &lt;strong&gt;여사건(일어나지 않을 확률)을 곱해&lt;/strong&gt; 구한다.$P ( T ) = 1 - ( 1 - 0.1 ) ( 1 - 0.15 ) ( 1 - 0.1 ) = 1 - 0.9 \times 0.85 \times 0.9 = 1 - 0.6885 = 0.3115$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;게이트별 확률 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P = P_{1} \times P_{2} \times \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나야&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;OR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P = 1 - ( 1 - P_{1} ) ( 1 - P_{2} ) \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하나만 일어나도&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$1 - 0.9 \times 0.85 \times 0.9 = 0.3115$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
         <is>
-          <t>② 0.35 는 세 확률을 그냥 더한 값에 가깝다.&lt;br&gt;③ 0.496 은 계산과 맞지 않는다.&lt;br&gt;④ 0.9985 는 여사건을 반대로 잡은 값이다.</t>
+          <t>② 0.35는 세 확률을 그냥 더한 값에 가깝다.&lt;br&gt;③ 0.496은 계산과 맞지 않는다.&lt;br&gt;④ 0.9985는 여사건을 반대로 잡은 값이다.</t>
         </is>
       </c>
       <c r="AI23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FT도의 정상사상 발생확률&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;OR 는 「곱해서 1 에서 뺀다」, AND 는 「그냥 곱한다」&lt;/strong&gt; 두 가지뿐이다 — &lt;strong&gt;확률이 작을 때 OR 는 대략 합에 가깝고 AND 는 훨씬 작아진다&lt;/strong&gt;는 것으로 검산한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;OR 는 1 − 여사건의 곱&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FT도의 정상사상 발생확률&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;OR는 「곱해서 1에서 뺀다」, AND는 「그냥 곱한다」&lt;/strong&gt; 두 가지뿐이다 — &lt;strong&gt;확률이 작을 때 OR는 대략 합에 가깝고 AND는 훨씬 작아진다&lt;/strong&gt;는 것으로 검산한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;OR는 1 − 여사건의 곱&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="V30" s="32" t="inlineStr">
         <is>
-          <t>( ㉠ ) : FTA 와 동일의 논리적 방법을 사용하여 관리, 설계, 생산, 보전 등에 대한 넓은 범위에 걸쳐 안전성을 확보하려는 시스템안전 프로그램&lt;br&gt;( ㉡ ) : 사고 시나리오에서 연속된 사건들의 발생 경로를 파악하고 평가하기 위한 귀납적이고 정량적인 시스템안전 프로그램</t>
+          <t>( ㉠ ) : FTA와 동일의 논리적 방법을 사용하여 관리, 설계, 생산, 보전 등에 대한 넓은 범위에 걸쳐 안전성을 확보하려는 시스템안전 프로그램&lt;br&gt;( ㉡ ) : 사고 시나리오에서 연속된 사건들의 발생 경로를 파악하고 평가하기 위한 귀납적이고 정량적인 시스템안전 프로그램</t>
         </is>
       </c>
       <c r="W30" s="32" t="inlineStr"/>
@@ -4930,17 +4930,17 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;㉠ 은 MORT, ㉡ 은 ETA&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;시스템 위험분석 기법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MORT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA 와 같은 논리를 써서 관리·설계·생산·보전까지 넓게 안전성을 확보&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;㉠&lt;/u&gt; · 원자력산업에서 나왔다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ETA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사고 시나리오에서 이어지는 사건의 경로를 따라가며 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;㉡ · 귀납적 · 정량적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PHA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템 개발 초기에 위험요소의 위험수준을 개략적으로 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;예비위험분석&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FTA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상사상에서 거꾸로 원인을 찾아 내려간다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연역적 · 정량적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;㉠ 은 MORT, ㉡ 은 ETA&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;시스템 위험분석 기법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MORT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA와 같은 논리를 써서 관리·설계·생산·보전까지 넓게 안전성을 확보&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;㉠&lt;/u&gt; · 원자력산업에서 나왔다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ETA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사고 시나리오에서 이어지는 사건의 경로를 따라가며 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;㉡ · 귀납적 · 정량적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PHA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템 개발 초기에 위험요소의 위험수준을 개략적으로 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;예비위험분석&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FTA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상사상에서 거꾸로 원인을 찾아 내려간다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연역적 · 정량적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
         <is>
-          <t>① ㉠ 을 PHA 로 보면 「넓은 범위에 걸쳐 안전성을 확보」와 맞지 않는다.&lt;br&gt;② ㉠ 을 ETA 로 보면 ㉡ 의 설명과 겹친다.&lt;br&gt;④ ㉡ 을 PHA 로 보면 「연속된 사건의 경로」와 맞지 않는다.</t>
+          <t>① ㉠ 을 PHA로 보면 「넓은 범위에 걸쳐 안전성을 확보」와 맞지 않는다.&lt;br&gt;② ㉠ 을 ETA로 보면 ㉡ 의 설명과 겹친다.&lt;br&gt;④ ㉡ 을 PHA로 보면 「연속된 사건의 경로」와 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;MORT 와 ETA&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;㉡ 의 「연속된 사건들의 발생 경로」가 곧 사상수(ETA)&lt;/strong&gt;다 — &lt;strong&gt;여기서 ㉡ 이 정해지면 ③ 하나만 남는다&lt;/strong&gt;. &lt;strong&gt;FTA 는 거꾸로 내려가는 연역, ETA 는 앞으로 나아가는 귀납&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;MORT 는 넓은 관리, ETA 는 사건의 경로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;MORT와 ETA&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;㉡ 의 「연속된 사건들의 발생 경로」가 곧 사상수(ETA)&lt;/strong&gt;다 — &lt;strong&gt;여기서 ㉡ 이 정해지면 ③ 하나만 남는다&lt;/strong&gt;. &lt;strong&gt;FTA는 거꾸로 내려가는 연역, ETA는 앞으로 나아가는 귀납&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;MORT는 넓은 관리, ETA는 사건의 경로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① FTA 는 정상사상의 원인을 거슬러 올라가는 기법이다.&lt;br&gt;② ETA 는 초기사상에서 앞으로의 경로를 따라가는 기법이다.&lt;br&gt;③ FHA 는 서브시스템 조합에서 생기는 결함을 보는 기법이다.</t>
+          <t>① FTA는 정상사상의 원인을 거슬러 올라가는 기법이다.&lt;br&gt;② ETA는 초기사상에서 앞으로의 경로를 따라가는 기법이다.&lt;br&gt;③ FHA는 서브시스템 조합에서 생기는 결함을 보는 기법이다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="AH32" s="32" t="inlineStr">
         <is>
-          <t>① 0.91 은 계산과 맞지 않는다.&lt;br&gt;② 0.93 도 그렇다.&lt;br&gt;④ 0.99 는 타이어 하나의 신뢰도다.</t>
+          <t>① 0.91은 계산과 맞지 않는다.&lt;br&gt;② 0.93 도 그렇다.&lt;br&gt;④ 0.99는 타이어 하나의 신뢰도다.</t>
         </is>
       </c>
       <c r="AI32" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;직렬 시스템의 신뢰도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;타이어 하나가 터지면 차가 못 간다&lt;/strong&gt; — 그래서 직렬이다. &lt;strong&gt;0.99 를 네 번 곱하면 약 0.96&lt;/strong&gt;으로, &lt;strong&gt;하나짜리보다 조금 낮아진다&lt;/strong&gt;는 방향만 맞아도 답이 골라진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;직렬은 곱셈, 0.99⁴ ≒ 0.96&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;직렬 시스템의 신뢰도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;타이어 하나가 터지면 차가 못 간다&lt;/strong&gt; — 그래서 직렬이다. &lt;strong&gt;0.99를 네 번 곱하면 약 0.96&lt;/strong&gt;으로, &lt;strong&gt;하나짜리보다 조금 낮아진다&lt;/strong&gt;는 방향만 맞아도 답이 골라진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;직렬은 곱셈, 0.99⁴ ≒ 0.96&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
-          <t>① 0.698 은 계산과 맞지 않는다.&lt;br&gt;② 0.798 도 그렇다.&lt;br&gt;③ 0.898 도 그렇다.</t>
+          <t>① 0.698은 계산과 맞지 않는다.&lt;br&gt;② 0.798 도 그렇다.&lt;br&gt;③ 0.898 도 그렇다.</t>
         </is>
       </c>
       <c r="AI33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가용도(availability)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;고장률이 수리율보다 훨씬 작으므로 가용도는 1 에 아주 가깝다&lt;/strong&gt; — &lt;strong&gt;네 보기 중 가장 큰 값&lt;/strong&gt;을 고르면 된다. &lt;strong&gt;분자에 수리율이 오는 것&lt;/strong&gt;만 헷갈리지 않으면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가용도 = 수리율 ÷ (고장률 + 수리율)&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;가용도(availability)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;고장률이 수리율보다 훨씬 작으므로 가용도는 1에 아주 가깝다&lt;/strong&gt; — &lt;strong&gt;네 보기 중 가장 큰 값&lt;/strong&gt;을 고르면 된다. &lt;strong&gt;분자에 수리율이 오는 것&lt;/strong&gt;만 헷갈리지 않으면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가용도 = 수리율 ÷ (고장률 + 수리율)&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="AG36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;소음에 적응된 사람을 배치&lt;/strong&gt; 하는 것은 &lt;strong&gt;소음을 그대로 두는&lt;/strong&gt; 것이라 대책이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;소음대책의 순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 소음원 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소음기 설치 · 진동부분의 표면적을 줄인다 · 저소음 기계로 바꾼다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 근본적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 전파경로 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차음벽 설치 · 거리를 둔다 · 흡음재를 붙인다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 수음자 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;귀마개·귀덮개 · 작업시간 단축&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;마지막 수단&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대책이 아닌 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소음에 적응된 인원 배치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소음은 그대로다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;소음에 적응된 사람을 배치&lt;/strong&gt;하는 것은 &lt;strong&gt;소음을 그대로 두는&lt;/strong&gt; 것이라 대책이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;소음대책의 순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 소음원 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소음기 설치 · 진동부분의 표면적을 줄인다 · 저소음 기계로 바꾼다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 근본적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 전파경로 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차음벽 설치 · 거리를 둔다 · 흡음재를 붙인다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 수음자 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;귀마개·귀덮개 · 작업시간 단축&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;마지막 수단&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대책이 아닌 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소음에 적응된 인원 배치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소음은 그대로다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH36" s="32" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="AH38" s="32" t="inlineStr">
         <is>
-          <t>① Omission error 는 해야 할 것을 하지 않은 오류다.&lt;br&gt;② Sequential error 는 순서를 틀린 오류다.&lt;br&gt;④ Commission error 는 하기는 했으나 잘못한 오류다.</t>
+          <t>① Omission error는 해야 할 것을 하지 않은 오류다.&lt;br&gt;② Sequential error는 순서를 틀린 오류다.&lt;br&gt;④ Commission error는 하기는 했으나 잘못한 오류다.</t>
         </is>
       </c>
       <c r="AI38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;휴먼 에러의 심리적 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「불필요한」이라는 낱말이 곧 여분(extraneous)&lt;/strong&gt;이다 — &lt;strong&gt;Commission 은 「할 일을 잘못한 것」이고 Extraneous 는 「할 일이 아니었던 것」&lt;/strong&gt;이라는 데서 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;불필요한 작업은 Extraneous error&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;휴먼 에러의 심리적 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「불필요한」이라는 낱말이 곧 여분(extraneous)&lt;/strong&gt;이다 — &lt;strong&gt;Commission은 「할 일을 잘못한 것」이고 Extraneous는 「할 일이 아니었던 것」&lt;/strong&gt;이라는 데서 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;불필요한 작업은 Extraneous error&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AI40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;차폐효과&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「차폐(遮蔽)」는 가린다&lt;/strong&gt;는 뜻이다 — &lt;strong&gt;가리면 잘 안 들리는 것이 당연&lt;/strong&gt; 하다. &lt;strong&gt;「감도가 증가」라고 뒤집어 놓은 보기&lt;/strong&gt;만 골라내면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;차폐효과는 감도가 떨어지는 현상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;차폐효과&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「차폐(遮蔽)」는 가린다&lt;/strong&gt;는 뜻이다 — &lt;strong&gt;가리면 잘 안 들리는 것이 당연&lt;/strong&gt;하다. &lt;strong&gt;「감도가 증가」라고 뒤집어 놓은 보기&lt;/strong&gt;만 골라내면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;차폐효과는 감도가 떨어지는 현상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6349,17 +6349,17 @@
       </c>
       <c r="AG41" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;MAA 는 소리가 어느 쪽에서 오는지 가려내는 각도&lt;/strong&gt;로 &lt;strong&gt;음원의 방향&lt;/strong&gt;에 관한 것이다. 나머지 셋은 소음 속에서 말이 얼마나 통하는지를 다룬다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;음성통신 관련 지수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AI&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;명료도 지수 — 말이 얼마나 또렷이 들리나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;음성통신&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PSIL&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;음성간섭수준 — 소음이 말을 얼마나 방해하나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;음성통신&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PNC&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;선호 소음판단 기준곡선 — 실내 소음이 견딜 만한가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;음성통신&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MAA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최소가청각도 — 방향을 가려낼 수 있는 가장 작은 각&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방향 분간&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;MAA는 소리가 어느 쪽에서 오는지 가려내는 각도&lt;/strong&gt;로 &lt;strong&gt;음원의 방향&lt;/strong&gt;에 관한 것이다. 나머지 셋은 소음 속에서 말이 얼마나 통하는지를 다룬다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;음성통신 관련 지수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AI&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;명료도 지수 — 말이 얼마나 또렷이 들리나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;음성통신&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PSIL&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;음성간섭수준 — 소음이 말을 얼마나 방해하나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;음성통신&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PNC&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;선호 소음판단 기준곡선 — 실내 소음이 견딜 만한가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;음성통신&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MAA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최소가청각도 — 방향을 가려낼 수 있는 가장 작은 각&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방향 분간&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH41" s="32" t="inlineStr">
         <is>
-          <t>① AI 는 명료도 지수로 음성통신에 관한 것이다.&lt;br&gt;③ PSIL 은 음성간섭수준으로 그렇다.&lt;br&gt;④ PNC 도 실내 소음 기준으로 그렇다.</t>
+          <t>① AI는 명료도 지수로 음성통신에 관한 것이다.&lt;br&gt;③ PSIL은 음성간섭수준으로 그렇다.&lt;br&gt;④ PNC 도 실내 소음 기준으로 그렇다.</t>
         </is>
       </c>
       <c r="AI41" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;음성통신 관련 지수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;셋은 「말이 통하는가」, 하나는 「어디서 나는 소리인가」&lt;/strong&gt;다 — &lt;strong&gt;이름에 Speech · Noise 가 들어간 쪽이 음성통신&lt;/strong&gt;이고 &lt;strong&gt;Angle 이 들어간 것만 방향&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;MAA 만 방향에 관한 지수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;음성통신 관련 지수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;셋은 「말이 통하는가」, 하나는 「어디서 나는 소리인가」&lt;/strong&gt;다 — &lt;strong&gt;이름에 Speech · Noise가 들어간 쪽이 음성통신&lt;/strong&gt;이고 &lt;strong&gt;Angle이 들어간 것만 방향&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;MAA 만 방향에 관한 지수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6478,17 +6478,17 @@
       </c>
       <c r="AG42" s="32" t="inlineStr">
         <is>
-          <t>$$H = \log_{2} n = \log_{2} 4 = 2 \, \mathrm{bit}$$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정보량의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대안이 같은 확률일 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$H = \log_{2} n$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대안마다 확률이 다를 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$H = \sum p_{i} \log_{2} ( \dfrac{1}{p}_{i} )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2택 1 → 1 bit, 4택 1 → 2 bit, 8택 1 → 3 bit&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 byte = 8 bit&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;byte 는 정보량 문제의 함정&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$$H = \log_{2} n = \log_{2} 4 = 2 \, \mathrm{bit}$$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정보량의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대안이 같은 확률일 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$H = \log_{2} n$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대안마다 확률이 다를 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$H = \sum p_{i} \log_{2} ( \dfrac{1}{p}_{i} )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2택 1 → 1 bit, 4택 1 → 2 bit, 8택 1 → 3 bit&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 byte = 8 bit&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;byte는 정보량 문제의 함정&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH42" s="32" t="inlineStr">
         <is>
-          <t>② 4 bit 는 16택 1 의 정보량이다.&lt;br&gt;③ 2 byte 는 16 bit 로 자릿수가 다르다.&lt;br&gt;④ 4 byte 는 32 bit 다.</t>
+          <t>② 4 bit는 16택 1의 정보량이다.&lt;br&gt;③ 2 byte는 16 bit로 자릿수가 다르다.&lt;br&gt;④ 4 byte는 32 bit다.</t>
         </is>
       </c>
       <c r="AI42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정보량(bit)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;2 를 몇 번 곱해야 대안 수가 되는가&lt;/strong&gt;가 정보량이다 — &lt;strong&gt;4 = 2², 그래서 2 bit&lt;/strong&gt;다. &lt;strong&gt;byte 로 된 보기는 단위만 바꿔 놓은 함정&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;4택 1 은 2 bit&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정보량(bit)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;2를 몇 번 곱해야 대안 수가 되는가&lt;/strong&gt;가 정보량이다 — &lt;strong&gt;4 = 2², 그래서 2 bit&lt;/strong&gt;다. &lt;strong&gt;byte로 된 보기는 단위만 바꿔 놓은 함정&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;4택 1은 2 bit&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AG48" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방호울식&lt;/strong&gt;이다. &lt;strong&gt;아예 손이 들어갈 틈을 없앤&lt;/strong&gt; 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;No hand in die 와 Hand in die&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;No hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전울(방호울) 부착 · 안전금형 · 전용 프레스 · 자동송급장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손이 들어갈 수 없다&lt;/u&gt; · 본질적 안전화&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가드식 · 수인식 · 손쳐내기식 · 양수조작식 · 광전자식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손은 들어가되 다치지 않게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;방호울식&lt;/strong&gt;이다. &lt;strong&gt;아예 손이 들어갈 틈을 없앤&lt;/strong&gt; 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;No hand in die와 Hand in die&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;No hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전울(방호울) 부착 · 안전금형 · 전용 프레스 · 자동송급장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손이 들어갈 수 없다&lt;/u&gt; · 본질적 안전화&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가드식 · 수인식 · 손쳐내기식 · 양수조작식 · 광전자식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손은 들어가되 다치지 않게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH48" s="32" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="AH51" s="32" t="inlineStr">
         <is>
-          <t>② Fail passive 는 고장 시 정지하는 단계다.&lt;br&gt;③ Fail active 는 경보를 내며 잠시 운전하는 단계다.&lt;br&gt;④ Fail operational 은 고칠 때까지 운전을 이어 가는 단계다.</t>
+          <t>② Fail passive는 고장 시 정지하는 단계다.&lt;br&gt;③ Fail active는 경보를 내며 잠시 운전하는 단계다.&lt;br&gt;④ Fail operational은 고칠 때까지 운전을 이어 가는 단계다.</t>
         </is>
       </c>
       <c r="AI51" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;페일 세이프의 기능적 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;페일 세이프는 「기계가 고장 났을 때」, 풀 프루프는 「사람이 잘못했을 때」&lt;/strong&gt;다 — &lt;strong&gt;세 보기가 모두 fail 로 시작&lt;/strong&gt; 하고 하나만 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;풀 프루프는 사람 쪽, 페일 세이프는 기계 쪽&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;페일 세이프의 기능적 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;페일 세이프는 「기계가 고장 났을 때」, 풀 프루프는 「사람이 잘못했을 때」&lt;/strong&gt;다 — &lt;strong&gt;세 보기가 모두 fail로 시작&lt;/strong&gt;하고 하나만 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;풀 프루프는 사람 쪽, 페일 세이프는 기계 쪽&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="AG54" s="32" t="inlineStr">
         <is>
-          <t>손쳐내기식은 &lt;strong&gt;120SPM 이하&lt;/strong&gt;에서 쓴다. &lt;strong&gt;빠른 프레스에는 쓸 수 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;손쳐내기식·수인식의 적용 범위&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;적용&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손쳐내기식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;슬라이드 행정수 120SPM 이하, 행정길이 40mm 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「300SPM 이상」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수인식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;슬라이드 행정수 100SPM 이하, 행정길이 50mm 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방호판 폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금형 폭의 1/2 이상, 300mm 를 넘으면 300mm 로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밀어내는 위치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하행정거리의 3/4 위치에서 손을 완전히 밀어낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>손쳐내기식은 &lt;strong&gt;120SPM 이하&lt;/strong&gt;에서 쓴다. &lt;strong&gt;빠른 프레스에는 쓸 수 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;손쳐내기식·수인식의 적용 범위&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;적용&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손쳐내기식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;슬라이드 행정수 120SPM 이하, 행정길이 40mm 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「300SPM 이상」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수인식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;슬라이드 행정수 100SPM 이하, 행정길이 50mm 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방호판 폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금형 폭의 1/2 이상, 300mm를 넘으면 300mm로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밀어내는 위치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하행정거리의 3/4 위치에서 손을 완전히 밀어낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH54" s="32" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="AH61" s="32" t="inlineStr">
         <is>
-          <t>① 0.6m 이내는 무릎 조작식이다.&lt;br&gt;② 0.8m 는 복부 조작식의 아래 한계다.&lt;br&gt;③ 1.1m 는 복부 조작식의 위 한계다.</t>
+          <t>① 0.6m 이내는 무릎 조작식이다.&lt;br&gt;② 0.8m는 복부 조작식의 아래 한계다.&lt;br&gt;③ 1.1m는 복부 조작식의 위 한계다.</t>
         </is>
       </c>
       <c r="AI61" s="32" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="AI62" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;롤러기 급정지장치의 설치 위치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;배꼽 높이는 대략 1m 안팎&lt;/strong&gt;이다 — &lt;strong&gt;1,200 ~ 1,400mm 는 가슴에서 어깨&lt;/strong&gt;라 배로 누를 수 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;복부 조작식은 800 ~ 1,100mm&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;롤러기 급정지장치의 설치 위치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;배꼽 높이는 대략 1m 안팎&lt;/strong&gt;이다 — &lt;strong&gt;1,200 ~ 1,400mm는 가슴에서 어깨&lt;/strong&gt;라 배로 누를 수 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;복부 조작식은 800 ~ 1,100mm&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;누전차단기의 설치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;전압 변동 허용범위는 「위아래로 조금씩」&lt;/strong&gt;이다 — &lt;strong&gt;85 ~ 110% 는 −15%, +10%&lt;/strong&gt;로 좁다. &lt;strong&gt;75 ~ 120% 는 지나치게 넓어&lt;/strong&gt; 그럴듯해 보여도 틀렸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누전차단기 전압 변동 범위는 85 ~ 110%&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;누전차단기의 설치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;전압 변동 허용범위는 「위아래로 조금씩」&lt;/strong&gt;이다 — &lt;strong&gt;85 ~ 110%는 −15%, +10%&lt;/strong&gt;로 좁다. &lt;strong&gt;75 ~ 120%는 지나치게 넓어&lt;/strong&gt; 그럴듯해 보여도 틀렸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누전차단기 전압 변동 범위는 85 ~ 110%&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="AH64" s="32" t="inlineStr">
         <is>
-          <t>① 0.5 kV 는 느끼지 못하는 정도다.&lt;br&gt;③ 5.5 kV 는 이미 팔뚝까지 아픈 수준이다.&lt;br&gt;④ 8.0 kV 는 더 강하다.</t>
+          <t>① 0.5 kV는 느끼지 못하는 정도다.&lt;br&gt;③ 5.5 kV는 이미 팔뚝까지 아픈 수준이다.&lt;br&gt;④ 8.0 kV는 더 강하다.</t>
         </is>
       </c>
       <c r="AI64" s="32" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="AG65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;절연용 보호구는 작업자가 몸에 걸치는 것&lt;/strong&gt;이라, &lt;strong&gt;기계가 전선에 닿을 위험&lt;/strong&gt;을 막지 못한다. 여기서는 &lt;strong&gt;전선 쪽에 씌우는 방호구&lt;/strong&gt; 라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가공전선 접근 작업의 조치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;해당 충전전로를 이설한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;감전 위험을 방지하기 위한 방책을 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;해당 충전전로에 절연용 방호구를 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전선 쪽에 씌운다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위 셋이 어려우면 감시인을 두고 작업을 감시하게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연용 보호구 착용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람이 걸치는 것 — 이 조항의 조치가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;절연용 보호구는 작업자가 몸에 걸치는 것&lt;/strong&gt;이라, &lt;strong&gt;기계가 전선에 닿을 위험&lt;/strong&gt;을 막지 못한다. 여기서는 &lt;strong&gt;전선 쪽에 씌우는 방호구&lt;/strong&gt;라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가공전선 접근 작업의 조치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;해당 충전전로를 이설한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;감전 위험을 방지하기 위한 방책을 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;해당 충전전로에 절연용 방호구를 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전선 쪽에 씌운다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위 셋이 어려우면 감시인을 두고 작업을 감시하게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연용 보호구 착용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람이 걸치는 것 — 이 조항의 조치가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH65" s="32" t="inlineStr">
@@ -9703,17 +9703,17 @@
       </c>
       <c r="AG67" s="32" t="inlineStr">
         <is>
-          <t>$$I = \dfrac{165}{\sqrt{T}} = \dfrac{165}{\sqrt{1}} = 165 \, \mathrm{mA}$$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;달지엘(Dalziel)의 심실세동전류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I = \dfrac{165}{\sqrt{T}} \, [ \mathrm{mA} ]$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T 는 통전시간(초), 1 ~ 5초&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000명 중 5명이 심실세동을 일으키는 값&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T = 1초&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;165 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험한계에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = I^{2} R T = ( 0.165 )^{2} \times 500 \times 1 \fallingdotseq 13.6 \, J$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$$I = \dfrac{165}{\sqrt{T}} = \dfrac{165}{\sqrt{1}} = 165 \, \mathrm{mA}$$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;달지엘(Dalziel)의 심실세동전류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I = \dfrac{165}{\sqrt{T}} \, [ \mathrm{mA} ]$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T는 통전시간(초), 1 ~ 5초&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000명 중 5명이 심실세동을 일으키는 값&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T = 1초&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;165 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험한계에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = I^{2} R T = ( 0.165 )^{2} \times 500 \times 1 \fallingdotseq 13.6 \, J$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH67" s="32" t="inlineStr">
         <is>
-          <t>② 105mA 는 계산과 맞지 않는다.&lt;br&gt;③ 50mA 는 심실세동 이전 단계의 값이다.&lt;br&gt;④ 0.5A 는 500mA 로 훨씬 크다.</t>
+          <t>② 105mA는 계산과 맞지 않는다.&lt;br&gt;③ 50mA는 심실세동 이전 단계의 값이다.&lt;br&gt;④ 0.5A는 500mA로 훨씬 크다.</t>
         </is>
       </c>
       <c r="AI67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;심실세동전류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;165 라는 수와 「√T 로 나눈다」&lt;/strong&gt; 두 가지만 외우면 된다 — &lt;strong&gt;통전시간이 길수록 더 작은 전류로도 심실세동&lt;/strong&gt;이 일어난다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;심실세동전류 = 165 ÷ √T mA&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;심실세동전류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;165라는 수와 「√T로 나눈다」&lt;/strong&gt; 두 가지만 외우면 된다 — &lt;strong&gt;통전시간이 길수록 더 작은 전류로도 심실세동&lt;/strong&gt;이 일어난다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;심실세동전류 = 165 ÷ √T mA&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전압의 구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;교류와 직류가 다른 곳은 저압·고압의 경계뿐&lt;/strong&gt;이다 — &lt;strong&gt;교류 1, 직류 1.5&lt;/strong&gt; . &lt;strong&gt;특고압 경계 7kV 는 둘이 같다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;저압은 교류 1kV, 직류 1.5kV 이하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 2021년 개정된 한국전기설비규정(KEC)의 구분이다. 예전의 「저압 : 직류 750V 이하, 교류 600V 이하」와 다르니 옛 교재의 값을 그대로 쓰지 않는다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전압의 구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;교류와 직류가 다른 곳은 저압·고압의 경계뿐&lt;/strong&gt;이다 — &lt;strong&gt;교류 1, 직류 1.5&lt;/strong&gt; . &lt;strong&gt;특고압 경계 7kV는 둘이 같다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;저압은 교류 1kV, 직류 1.5kV 이하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 2021년 개정된 한국전기설비규정(KEC)의 구분이다. 예전의 「저압 : 직류 750V 이하, 교류 600V 이하」와 다르니 옛 교재의 값을 그대로 쓰지 않는다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10079,12 +10079,12 @@
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① Ⅰ등급 20m 는 맞다.&lt;br&gt;② Ⅱ등급 30m 도 맞다.&lt;br&gt;④ Ⅳ등급 60m 도 맞다.</t>
+          <t>① Ⅰ등급 20m는 맞다.&lt;br&gt;② Ⅱ등급 30m 도 맞다.&lt;br&gt;④ Ⅳ등급 60m 도 맞다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;회전구체법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;20 · 30 · 45 · 60 — 간격이 10 · 15 · 15&lt;/strong&gt;로 늘어난다 — &lt;strong&gt;셋째만 40 으로 바꿔 놓으면 「10씩 늘어나는」 가짜 규칙&lt;/strong&gt;처럼 보인다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;회전구체 반지름 20 · 30 · 45 · 60&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;회전구체법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;20 · 30 · 45 · 60 — 간격이 10 · 15 · 15&lt;/strong&gt;로 늘어난다 — &lt;strong&gt;셋째만 40으로 바꿔 놓으면 「10씩 늘어나는」 가짜 규칙&lt;/strong&gt;처럼 보인다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;회전구체 반지름 20 · 30 · 45 · 60&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AG71" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;내압(耐壓) 방폭구조&lt;/strong&gt;다. &lt;strong&gt;틈으로 새 나오는 화염이 식어&lt;/strong&gt;밖에 불이 붙지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭구조의 종류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구조&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내압 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;d&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;용기가 폭발압력을 견디고, 틈이 화염을 식힌다&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;p&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안의 압력을 밖보다 높여 가스가 못 들어오게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유입 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;o&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;기름 속에 잠가 둔다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전증 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;e&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정상 상태에서 불꽃이 안 생기게 여유를 더 준다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;본질안전 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ia, ib&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;점화에 필요한 에너지 자체를 못 넘게&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;내압(耐壓) 방폭구조&lt;/strong&gt;다. &lt;strong&gt;틈으로 새 나오는 화염이 식어&lt;/strong&gt; 밖에 불이 붙지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭구조의 종류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구조&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내압 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;d&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;용기가 폭발압력을 견디고, 틈이 화염을 식힌다&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;p&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안의 압력을 밖보다 높여 가스가 못 들어오게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유입 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;o&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;기름 속에 잠가 둔다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전증 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;e&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정상 상태에서 불꽃이 안 생기게 여유를 더 준다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;본질안전 방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ia, ib&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;점화에 필요한 에너지 자체를 못 넘게&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH71" s="32" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="AG73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;틈을 좁혀야 새 나가는 화염이 식어&lt;/strong&gt; 밖의 가스에 불이 붙지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;화염일주한계(안전간극)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무엇&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;화염이 틈을 빠져나가지 못하는 최대 틈&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;MESG&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;좁히는 까닭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빠져나가며 열을 빼앗겨 식는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭발등급&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ⅡA 0.9mm 초과 · ⅡB 0.5 ~ 0.9mm · ⅡC 0.5mm 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ⅡC 가 가장 위험&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡC 의 보기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 · 아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;틈을 좁혀야 새 나가는 화염이 식어&lt;/strong&gt; 밖의 가스에 불이 붙지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;화염일주한계(안전간극)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무엇&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;화염이 틈을 빠져나가지 못하는 최대 틈&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;MESG&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;좁히는 까닭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빠져나가며 열을 빼앗겨 식는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭발등급&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ⅡA 0.9mm 초과 · ⅡB 0.5 ~ 0.9mm · ⅡC 0.5mm 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ⅡC가 가장 위험&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡC의 보기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 · 아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH73" s="32" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="AI73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전간극(화염일주한계)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;좁고 긴 틈을 지나며 뜨거운 가스가 벽에 열을 빼앗긴다&lt;/strong&gt; — &lt;strong&gt;그래서 밖에 나올 때는 이미 발화점 아래&lt;/strong&gt;다. &lt;strong&gt;수소·아세틸렌처럼 간극이 좁은 가스가 가장 위험&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전간극을 좁히는 것은 화염 전파를 막기 위해&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전간극(화염일주한계)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;좁고 긴 틈을 지나며 뜨거운 가스가 벽에 열을 빼앗긴다&lt;/strong&gt; — &lt;strong&gt;그래서 밖에 나올 때는 이미 발화점 아래&lt;/strong&gt;다. &lt;strong&gt;수소·아세틸렌처럼 간극이 좁은 가스가 가장 위험&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전간극을 좁히는 것은 화염 전파를 막기 위해&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10590,17 +10590,17 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>$$E = \dfrac{1}{2} CV^{2} = \dfrac{1}{2} \times 120 \times 10^{-12} \times ( 3 {,} 000 )^{2} = 5.4 \times 10^{-4} \, J = 0.54 \, \mathrm{mJ}$$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전기 방전에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$E = \dfrac{1}{2} CV^{2} = \dfrac{1}{2} QV$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C 는 F, V 는 V, E 는 J&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{1}{2} \times 120 p \times 3 {,} 000^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;120 pF = 120 × 10⁻¹² F&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;결과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5.4 × 10⁻⁴ J = 0.54 mJ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이만한 에너지로 불이 붙었으니 최소 착화에너지는 이보다 크지 않다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상한치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$$E = \dfrac{1}{2} CV^{2} = \dfrac{1}{2} \times 120 \times 10^{-12} \times ( 3 {,} 000 )^{2} = 5.4 \times 10^{-4} \, J = 0.54 \, \mathrm{mJ}$$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전기 방전에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$E = \dfrac{1}{2} CV^{2} = \dfrac{1}{2} QV$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C는 F, V는 V, E는 J&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{1}{2} \times 120 p \times 3 {,} 000^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;120 pF = 120 × 10⁻¹² F&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;결과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5.4 × 10⁻⁴ J = 0.54 mJ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이만한 에너지로 불이 붙었으니 최소 착화에너지는 이보다 크지 않다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상한치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>② 0.54J 는 단위가 1,000배 크다.&lt;br&gt;③ 1.08mJ 은 ½ 을 빠뜨린 값이다.&lt;br&gt;④ 1.08J 은 두 잘못을 함께 저지른 값이다.</t>
+          <t>② 0.54J는 단위가 1,000배 크다.&lt;br&gt;③ 1.08mJ은 ½ 을 빠뜨린 값이다.&lt;br&gt;④ 1.08J은 두 잘못을 함께 저지른 값이다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기 방전에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;½ 을 빠뜨리면 두 배, mJ 과 J 을 헷갈리면 1,000배&lt;/strong&gt; 어긋난다 — &lt;strong&gt;네 보기가 바로 그 두 함정&lt;/strong&gt;으로 짜여 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;E = ½CV², 120pF·3kV → 0.54mJ&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기 방전에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;½ 을 빠뜨리면 두 배, mJ과 J을 헷갈리면 1,000배&lt;/strong&gt; 어긋난다 — &lt;strong&gt;네 보기가 바로 그 두 함정&lt;/strong&gt;으로 짜여 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;E = ½CV², 120pF·3kV → 0.54mJ&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AI80" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기 제거용 접지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정전기는 전하량이 아주 작아&lt;/strong&gt; 웬만한 길만 있어도 빠져나간다 — &lt;strong&gt;감전방지용 10Ω 과 견주면 10만 배나 느슨&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;정전기 제거용 접지는 10⁶Ω 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기 제거용 접지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정전기는 전하량이 아주 작아&lt;/strong&gt; 웬만한 길만 있어도 빠져나간다 — &lt;strong&gt;감전방지용 10Ω 과 견주면 10만 배나 느슨&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;정전기 제거용 접지는 10⁶Ω 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="U87" s="32" t="inlineStr">
         <is>
-          <t>액화 프로판 310kg 을 내용적 50L 용기에 충전할 때 필요한 소요 용기의 수는 약 몇 개인가? (단, 액화 프로판의 가스정수는 2.35 이다.)</t>
+          <t>액화 프로판 310kg을 내용적 50L 용기에 충전할 때 필요한 소요 용기의 수는 약 몇 개인가? (단, 액화 프로판의 가스정수는 2.35이다.)</t>
         </is>
       </c>
       <c r="V87" s="32" t="inlineStr"/>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="AG87" s="32" t="inlineStr">
         <is>
-          <t>용기 한 개에 담을 수 있는 양은$W = \dfrac{V}{C} = \dfrac{50}{2.35} \fallingdotseq 21.3 \, \mathrm{kg}$$\text{용기 수} = \dfrac{310}{21.3} \fallingdotseq 14.6 \rightarrow 15 \, \text{개}$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;액화가스의 충전량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;용기 1개의 충전량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = \dfrac{V}{C}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;V 는 내용적(L), C 는 가스정수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 ÷ 2.35 ≒ 21.3 kg&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;용기 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;310 ÷ 21.3 ≒ 14.6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;올림해 15개&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;나머지가 남으면 한 개를 더 잡는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>용기 한 개에 담을 수 있는 양은$W = \dfrac{V}{C} = \dfrac{50}{2.35} \fallingdotseq 21.3 \, \mathrm{kg}$$\text{용기 수} = \dfrac{310}{21.3} \fallingdotseq 14.6 \rightarrow 15 \, \text{개}$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;액화가스의 충전량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;용기 1개의 충전량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = \dfrac{V}{C}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;V는 내용적(L), C는 가스정수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 ÷ 2.35 ≒ 21.3 kg&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;용기 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;310 ÷ 21.3 ≒ 14.6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;올림해 15개&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;나머지가 남으면 한 개를 더 잡는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH87" s="32" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="AI87" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;액화가스의 충전량&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「내용적 ÷ 가스정수」가 용기 하나에 담을 무게&lt;/strong&gt;다 — &lt;strong&gt;21.3kg 이라는 중간값을 답으로 착각하지 않도록&lt;/strong&gt; 조심한다. &lt;strong&gt;끝에 반드시 올림&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;용기 1개 충전량 = 내용적 ÷ 가스정수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;액화가스의 충전량&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「내용적 ÷ 가스정수」가 용기 하나에 담을 무게&lt;/strong&gt;다 — &lt;strong&gt;21.3kg이라는 중간값을 답으로 착각하지 않도록&lt;/strong&gt; 조심한다. &lt;strong&gt;끝에 반드시 올림&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;용기 1개 충전량 = 내용적 ÷ 가스정수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="AG89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;둘 다 산화반응&lt;/strong&gt;이다. &lt;strong&gt;녹스는 것은 느린 산화, 타는 것은 빠른 산화&lt;/strong&gt; 일 뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;산화반응의 두 얼굴&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;완만한 산화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;철이 녹슨다 · 기름이 산패한다 · 생물의 호흡&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빛과 열이 눈에 띄지 않는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;급격한 산화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;솜이 탄다 · 가스가 폭발한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산화의 뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산소와 결합한다 · 수소를 잃는다 · 전자를 잃는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;둘 다 산화반응&lt;/strong&gt;이다. &lt;strong&gt;녹스는 것은 느린 산화, 타는 것은 빠른 산화&lt;/strong&gt;일 뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;산화반응의 두 얼굴&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;완만한 산화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;철이 녹슨다 · 기름이 산패한다 · 생물의 호흡&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빛과 열이 눈에 띄지 않는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;급격한 산화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;솜이 탄다 · 가스가 폭발한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산화의 뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산소와 결합한다 · 수소를 잃는다 · 전자를 잃는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH89" s="32" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="AH93" s="32" t="inlineStr">
         <is>
-          <t>① 메탄은 약 9.5% 로 가장 높다.&lt;br&gt;② 프로판은 약 4.0% 다.&lt;br&gt;④ 아세틸렌은 약 7.7% 다.</t>
+          <t>① 메탄은 약 9.5%로 가장 높다.&lt;br&gt;② 프로판은 약 4.0%다.&lt;br&gt;④ 아세틸렌은 약 7.7%다.</t>
         </is>
       </c>
       <c r="AI93" s="32" t="inlineStr">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="U94" s="32" t="inlineStr">
         <is>
-          <t>다음 중 Halon 2402 의 화학식으로 옳은 것은?</t>
+          <t>다음 중 Halon 2402의 화학식으로 옳은 것은?</t>
         </is>
       </c>
       <c r="V94" s="32" t="inlineStr"/>
@@ -13166,7 +13166,7 @@
       </c>
       <c r="AG94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;C₂F₄Br₂&lt;/strong&gt;다. &lt;strong&gt;번호가 곧 C · F · Cl · Br 의 개수&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;할론 번호 읽는 법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;자리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;첫째&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C(탄소)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;둘째&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;F(불소)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;셋째&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Cl(염소)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;넷째&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Br(브롬)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;할론 2402&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C 2, F 4, Cl 0, Br 2 → C₂F₄Br₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;C₂F₄Br₂&lt;/strong&gt;다. &lt;strong&gt;번호가 곧 C · F · Cl · Br의 개수&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;할론 번호 읽는 법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;자리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;첫째&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C(탄소)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;둘째&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;F(불소)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;셋째&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Cl(염소)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;넷째&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Br(브롬)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;할론 2402&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C 2, F 4, Cl 0, Br 2 → C₂F₄Br₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH94" s="32" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="AI94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;할론 번호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「탄 · 불 · 염 · 브」 순서&lt;/strong&gt;다 — &lt;strong&gt;2402 는 C2 F4 Cl0 Br2&lt;/strong&gt; . &lt;strong&gt;0 인 자리는 아예 안 쓴다&lt;/strong&gt;는 것만 유의한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;할론 번호는 C·F·Cl·Br 개수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;할론 번호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「탄 · 불 · 염 · 브」 순서&lt;/strong&gt;다 — &lt;strong&gt;2402는 C2 F4 Cl0 Br2&lt;/strong&gt; . &lt;strong&gt;0 인 자리는 아예 안 쓴다&lt;/strong&gt;는 것만 유의한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;할론 번호는 C·F·Cl·Br 개수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="AH95" s="32" t="inlineStr">
         <is>
-          <t>② Vent stack 은 압력을 대기로 내보내는 설비다.&lt;br&gt;③ Blow down 은 보일러 수의 불순물을 빼내는 것이다.&lt;br&gt;④ Flame arrester 는 화염의 전파를 막는 장치다.</t>
+          <t>② Vent stack은 압력을 대기로 내보내는 설비다.&lt;br&gt;③ Blow down은 보일러 수의 불순물을 빼내는 것이다.&lt;br&gt;④ Flame arrester는 화염의 전파를 막는 장치다.</t>
         </is>
       </c>
       <c r="AI95" s="32" t="inlineStr">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="AH96" s="32" t="inlineStr">
         <is>
-          <t>① 하론 1031 은 F 가 0개, Cl 이 3개라는 뜻이다.&lt;br&gt;② 하론 1311 은 Cl 이 1개 더 있다는 뜻이다.&lt;br&gt;④ 하론 1310 은 Br 이 없다는 뜻이라 소화약제가 되지 못한다.</t>
+          <t>① 하론 1031은 F가 0개, Cl이 3개라는 뜻이다.&lt;br&gt;② 하론 1311은 Cl이 1개 더 있다는 뜻이다.&lt;br&gt;④ 하론 1310은 Br이 없다는 뜻이라 소화약제가 되지 못한다.</t>
         </is>
       </c>
       <c r="AI96" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;할론 번호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Br 이 없으면 소화 효과(부촉매 작용)가 없다&lt;/strong&gt; — &lt;strong&gt;마지막 자리가 0 인 「1310」은 그것만으로 지워진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;CF₃Br 은 하론 1301&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;할론 번호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Br이 없으면 소화 효과(부촉매 작용)가 없다&lt;/strong&gt; — &lt;strong&gt;마지막 자리가 0 인 「1310」은 그것만으로 지워진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;CF₃Br은 하론 1301&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13682,17 +13682,17 @@
       </c>
       <c r="AG98" s="32" t="inlineStr">
         <is>
-          <t>8% 를 $x$kg 이라 하면$x + y = 100 , \, \, 0.08 x + 0.05 y = 6$$0.08 x + 0.05 ( 100 - x ) = 6 \rightarrow 0.03 x = 1 \rightarrow x \fallingdotseq 33.3$따라서 &lt;strong&gt;8% 는 33.3kg, 5% 는 66.7kg&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;혼합 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전체 질량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;x + y = 100 kg&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;NaOH 질량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.08x + 0.05y = 6 kg&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;8% 용액&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;33.3 kg&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5% 용액&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;66.7 kg&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6% 는 5% 에 가까우므로 5% 쪽이 더 많다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 : 1&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>8%를 $x$kg이라 하면$x + y = 100 , \, \, 0.08 x + 0.05 y = 6$$0.08 x + 0.05 ( 100 - x ) = 6 \rightarrow 0.03 x = 1 \rightarrow x \fallingdotseq 33.3$따라서 &lt;strong&gt;8%는 33.3kg, 5%는 66.7kg&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;혼합 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전체 질량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;x + y = 100 kg&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;NaOH 질량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.08x + 0.05y = 6 kg&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;8% 용액&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;33.3 kg&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5% 용액&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;66.7 kg&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6%는 5%에 가까우므로 5% 쪽이 더 많다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 : 1&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH98" s="32" t="inlineStr">
         <is>
-          <t>① ①은 5% 와 8% 를 뒤바꾼 값이다.&lt;br&gt;② ②는 계산과 맞지 않는다.&lt;br&gt;④ ④도 그렇다.</t>
+          <t>① ①은 5%와 8%를 뒤바꾼 값이다.&lt;br&gt;② ②는 계산과 맞지 않는다.&lt;br&gt;④ ④도 그렇다.</t>
         </is>
       </c>
       <c r="AI98" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;용액의 혼합 계산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;목표 6% 는 5% 와 8% 사이에서 5% 쪽에 가깝다&lt;/strong&gt; — &lt;strong&gt;그러니 5% 용액이 더 많이 들어간다&lt;/strong&gt;. &lt;strong&gt;거리의 비가 2 : 1 이므로 양의 비는 그 반대인 2 : 1&lt;/strong&gt;로 5% 가 두 배다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;묽은 쪽에 가까우면 묽은 용액이 더 많이 든다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;용액의 혼합 계산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;목표 6%는 5%와 8% 사이에서 5% 쪽에 가깝다&lt;/strong&gt; — &lt;strong&gt;그러니 5% 용액이 더 많이 들어간다&lt;/strong&gt;. &lt;strong&gt;거리의 비가 2 : 1이므로 양의 비는 그 반대인 2 : 1&lt;/strong&gt;로 5%가 두 배다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;묽은 쪽에 가까우면 묽은 용액이 더 많이 든다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="AG103" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;너비 1.2m 이상의 계단참&lt;/strong&gt;을 둔다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가설계단의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하중 500kg/m² 이상, 안전율 4 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 m 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;급유용·보수용은 예외&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 3m 를 넘으면 3m 이내마다 너비 1.2m 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 1m 이상이면 개방된 쪽에 안전난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 제한&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;천장까지 2m 이상의 공간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;너비 1.2m 이상의 계단참&lt;/strong&gt;을 둔다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가설계단의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하중 500kg/m² 이상, 안전율 4 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 m 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;급유용·보수용은 예외&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 3m를 넘으면 3m 이내마다 너비 1.2m 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 1m 이상이면 개방된 쪽에 안전난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 제한&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;천장까지 2m 이상의 공간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH103" s="32" t="inlineStr">
         <is>
-          <t>① 3.5m 는 계단참 너비 기준이 아니다.&lt;br&gt;② 2.5m 도 그렇다.&lt;br&gt;④ 1.0m 는 계단의 폭 기준이다.</t>
+          <t>① 3.5m는 계단참 너비 기준이 아니다.&lt;br&gt;② 2.5m 도 그렇다.&lt;br&gt;④ 1.0m는 계단의 폭 기준이다.</t>
         </is>
       </c>
       <c r="AI103" s="32" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="AG104" s="32" t="inlineStr">
         <is>
-          <t>출제 당시 기준으로 띠장간격은 &lt;strong&gt;1.5m 이하&lt;/strong&gt; 였다. &lt;strong&gt;「2m 이하」가 틀린 보기&lt;/strong&gt; 였다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관비계 조립 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;띠장간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2m 이하(현행)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;출제 당시에는 1.5m 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;띠장 방향 1.85m 이하, 장선 방향 1.5m 이하(현행)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;출제 당시 띠장 방향 1.5 ~ 1.8m&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밑부분 보강&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맨 윗부분에서 31m 되는 지점 아래는 강관 2개로 묶는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비계기둥 사이 400kg 을 넘지 않게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>출제 당시 기준으로 띠장간격은 &lt;strong&gt;1.5m 이하&lt;/strong&gt; 였다. &lt;strong&gt;「2m 이하」가 틀린 보기&lt;/strong&gt; 였다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관비계 조립 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;띠장간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2m 이하(현행)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;출제 당시에는 1.5m 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;띠장 방향 1.85m 이하, 장선 방향 1.5m 이하(현행)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;출제 당시 띠장 방향 1.5 ~ 1.8m&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밑부분 보강&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맨 윗부분에서 31m 되는 지점 아래는 강관 2개로 묶는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비계기둥 사이 400kg을 넘지 않게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH104" s="32" t="inlineStr">
@@ -14458,7 +14458,7 @@
       </c>
       <c r="AI104" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;강관비계의 조립 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;31m 와 400kg 은 예나 지금이나 그대로&lt;/strong&gt;다 — &lt;strong&gt;바뀐 것은 띠장간격과 기둥 간격&lt;/strong&gt; 이니 그 둘만 새 값으로 갈아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;31m 아래는 강관 2개, 기둥 간 400kg&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 현행 기준은 띠장간격 2m 이하, 비계기둥 간격은 띠장 방향 1.85m 이하ㆍ장선 방향 1.5m 이하다. 이 문항은 개정 전 기준으로 출제되어 ①이 정답으로 처리되었다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;강관비계의 조립 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;31m와 400kg은 예나 지금이나 그대로&lt;/strong&gt;다 — &lt;strong&gt;바뀐 것은 띠장간격과 기둥 간격&lt;/strong&gt; 이니 그 둘만 새 값으로 갈아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;31m 아래는 강관 2개, 기둥 간 400kg&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 현행 기준은 띠장간격 2m 이하, 비계기둥 간격은 띠장 방향 1.85m 이하ㆍ장선 방향 1.5m 이하다. 이 문항은 개정 전 기준으로 출제되어 ①이 정답으로 처리되었다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="AG106" s="32" t="inlineStr">
         <is>
-          <t>진동기는 &lt;strong&gt;적절히 사용&lt;/strong&gt; 해야 한다. &lt;strong&gt;너무 많이 쓰면 재료가 분리되고 거푸집이 터진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;콘크리트 타설 안전수칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;수칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;타설순서는 계획에 따라 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;타설 중 거푸집·지보공의 이상 유무를 확인한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이상이 있으면 즉시 보강&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손수레는 천천히 운반해 거푸집에 충격을 주지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한곳에 몰아 붓지 않고 골고루 편다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;진동기는 적절히 사용한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「최대한 많이」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>진동기는 &lt;strong&gt;적절히 사용&lt;/strong&gt;해야 한다. &lt;strong&gt;너무 많이 쓰면 재료가 분리되고 거푸집이 터진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;콘크리트 타설 안전수칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;수칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;타설순서는 계획에 따라 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;타설 중 거푸집·지보공의 이상 유무를 확인한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이상이 있으면 즉시 보강&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손수레는 천천히 운반해 거푸집에 충격을 주지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한곳에 몰아 붓지 않고 골고루 편다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;진동기는 적절히 사용한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「최대한 많이」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH106" s="32" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="AI110" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;잠함 내부 굴착작업의 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;사람이 허리를 펴고 설 수 있는 높이&lt;/strong&gt; 라야 한다 — &lt;strong&gt;1.8m 는 성인 키에 가까운 값&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;잠함 내부 천장 높이는 1.8m 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;잠함 내부 굴착작업의 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;사람이 허리를 펴고 설 수 있는 높이&lt;/strong&gt;라야 한다 — &lt;strong&gt;1.8m는 성인 키에 가까운 값&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;잠함 내부 천장 높이는 1.8m 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15747,12 +15747,12 @@
       </c>
       <c r="AH114" s="32" t="inlineStr">
         <is>
-          <t>② 4m 는 기준값이 아니다.&lt;br&gt;③ 6m 도 그렇다.&lt;br&gt;④ 8m 도 그렇다.</t>
+          <t>② 4m는 기준값이 아니다.&lt;br&gt;③ 6m 도 그렇다.&lt;br&gt;④ 8m 도 그렇다.</t>
         </is>
       </c>
       <c r="AI114" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;화물자동차의 승강설비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;2m 는 추락재해의 경계선&lt;/strong&gt;으로 여러 조항에 되풀이해 나온다 — &lt;strong&gt;안전난간 · 작업발판 · 추락방호망 기준&lt;/strong&gt;도 모두 2m 를 기준으로 삼는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;짐 윗면 2m 이상이면 승강설비&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;화물자동차의 승강설비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;2m는 추락재해의 경계선&lt;/strong&gt;으로 여러 조항에 되풀이해 나온다 — &lt;strong&gt;안전난간 · 작업발판 · 추락방호망 기준&lt;/strong&gt;도 모두 2m를 기준으로 삼는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;짐 윗면 2m 이상이면 승강설비&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AH117" s="32" t="inlineStr">
         <is>
-          <t>① 문화재 0.2cm/sec 는 맞다.&lt;br&gt;② 주택·아파트 0.5cm/sec 도 맞다.&lt;br&gt;③ 상가 1.0cm/sec 도 맞다.</t>
+          <t>① 문화재 0.2cm/sec는 맞다.&lt;br&gt;② 주택·아파트 0.5cm/sec 도 맞다.&lt;br&gt;③ 상가 1.0cm/sec 도 맞다.</t>
         </is>
       </c>
       <c r="AI117" s="32" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="AH119" s="32" t="inlineStr">
         <is>
-          <t>① 10m/s 초과는 설치·해체 작업의 중지 기준이다.&lt;br&gt;③ 20m/s 는 기준값이 아니다.&lt;br&gt;④ 25m/s 도 그렇다.</t>
+          <t>① 10m/s 초과는 설치·해체 작업의 중지 기준이다.&lt;br&gt;③ 20m/s는 기준값이 아니다.&lt;br&gt;④ 25m/s 도 그렇다.</t>
         </is>
       </c>
       <c r="AI119" s="32" t="inlineStr">
@@ -16779,12 +16779,12 @@
       </c>
       <c r="AH122" s="32" t="inlineStr">
         <is>
-          <t>① 70cm 는 기준값이 아니다.&lt;br&gt;② 80cm 도 그렇다.&lt;br&gt;④ 100cm 도 그렇다.</t>
+          <t>① 70cm는 기준값이 아니다.&lt;br&gt;② 80cm 도 그렇다.&lt;br&gt;④ 100cm 도 그렇다.</t>
         </is>
       </c>
       <c r="AI122" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;하역작업장의 통로 폭&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;사람 한 명이 짐을 들고 지날 폭&lt;/strong&gt;이다 — &lt;strong&gt;90cm 라는 값을 「가설계단 폭 1m, 계단참 1.2m」와 나란히&lt;/strong&gt; 두고 외운다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;부두·안벽 통로 폭은 90cm 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;하역작업장의 통로 폭&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;사람 한 명이 짐을 들고 지날 폭&lt;/strong&gt;이다 — &lt;strong&gt;90cm라는 값을 「가설계단 폭 1m, 계단참 1.2m」와 나란히&lt;/strong&gt; 두고 외운다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;부두·안벽 통로 폭은 90cm 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
